--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488061_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488061_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.0502</v>
+        <v>10.2299</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3991</v>
+        <v>7.8877</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6511</v>
+        <v>2.3422</v>
       </c>
       <c r="G2" t="n">
         <v>4.6001</v>
@@ -610,13 +610,13 @@
         <v>2.9733</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1715</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2369</v>
+        <v>0.2517</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0654</v>
+        <v>-0.2435</v>
       </c>
       <c r="V2" t="n">
         <v>3.8376</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8778</v>
+        <v>7.1853</v>
       </c>
       <c r="E3" t="n">
-        <v>8.1823</v>
+        <v>7.9391</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3045</v>
+        <v>-0.7537</v>
       </c>
       <c r="G3" t="n">
         <v>0.7585</v>
@@ -688,13 +688,13 @@
         <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0329</v>
+        <v>0.3404</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2373</v>
+        <v>0.994</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2044</v>
+        <v>-0.6536</v>
       </c>
       <c r="V3" t="n">
         <v>4.1042</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2795</v>
+        <v>5.8867</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5616</v>
+        <v>4.0304</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7179</v>
+        <v>1.8562</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0572</v>
+        <v>7.2525</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6167</v>
+        <v>1.8612</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4404</v>
+        <v>5.3913</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2016</v>
+        <v>5.8497</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0007</v>
+        <v>2.1054</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2009</v>
+        <v>3.7443</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8556</v>
+        <v>1.4028</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3839</v>
+        <v>-0.2442</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2395</v>
+        <v>1.647</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9822</v>
+        <v>0.7929</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9822</v>
+        <v>2.7751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.251</v>
+        <v>-1.8218</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1638</v>
+        <v>-0.1036</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-1.7182</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0109</v>
+        <v>-0.337</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1962</v>
+        <v>0.2666</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2071</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.9156</v>
+        <v>4.4209</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3963</v>
+        <v>3.8714</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5193</v>
+        <v>0.5495</v>
       </c>
       <c r="G5" t="n">
-        <v>7.2525</v>
+        <v>4.0572</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8612</v>
+        <v>2.6167</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3913</v>
+        <v>1.4404</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8497</v>
+        <v>3.2016</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1054</v>
+        <v>3.0007</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7443</v>
+        <v>0.2009</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4028</v>
+        <v>0.8556</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2442</v>
+        <v>-0.3839</v>
       </c>
       <c r="O5" t="n">
-        <v>1.647</v>
+        <v>1.2395</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7929</v>
+        <v>1.9822</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7751</v>
+        <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.7928</v>
+        <v>-0.6076</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7377</v>
+        <v>0.4737</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.0551</v>
+        <v>-1.0813</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.337</v>
+        <v>-1.0109</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>0.1962</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6036</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7226</v>
+        <v>3.2477</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7636</v>
+        <v>3.0921</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.041</v>
+        <v>0.1556</v>
       </c>
       <c r="G6" t="n">
         <v>2.4888</v>
@@ -922,13 +922,13 @@
         <v>1.784</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5502</v>
+        <v>-1.0252</v>
       </c>
       <c r="T6" t="n">
-        <v>0.191</v>
+        <v>0.5195</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.7412</v>
+        <v>-1.5447</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3574</v>
+        <v>1.0964</v>
       </c>
       <c r="E7" t="n">
-        <v>1.802</v>
+        <v>0.6815</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5553</v>
+        <v>0.4149</v>
       </c>
       <c r="G7" t="n">
         <v>0.9549</v>
@@ -1000,13 +1000,13 @@
         <v>1.9822</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1089</v>
+        <v>0.848</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9788</v>
+        <v>0.8582</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1301</v>
+        <v>-0.0103</v>
       </c>
       <c r="V7" t="n">
         <v>0.4828</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1737</v>
+        <v>0.1208</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0003</v>
+        <v>-0.3059</v>
       </c>
       <c r="F8" t="n">
-        <v>0.174</v>
+        <v>0.4267</v>
       </c>
       <c r="G8" t="n">
         <v>-0.728</v>
@@ -1078,13 +1078,13 @@
         <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5577</v>
+        <v>0.5048</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7343</v>
+        <v>0.4287</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1766</v>
+        <v>0.0761</v>
       </c>
       <c r="V8" t="n">
         <v>0.1459</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0826</v>
+        <v>-0.0762</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7566000000000001</v>
+        <v>0.0813</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.326</v>
+        <v>-0.1576</v>
       </c>
       <c r="G9" t="n">
         <v>2.0386</v>
@@ -1156,13 +1156,13 @@
         <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.3105</v>
+        <v>-1.3041</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6864</v>
+        <v>0.1515</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.6241</v>
+        <v>-1.4556</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2071</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2465</v>
+        <v>-5.4398</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.373</v>
+        <v>-5.6786</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1265</v>
+        <v>0.2388</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1735</v>
@@ -1234,13 +1234,13 @@
         <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0477</v>
+        <v>0.8544</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7343</v>
+        <v>0.4287</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3134</v>
+        <v>0.4257</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3278</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>26.0477</v>
+        <v>26.6717</v>
       </c>
       <c r="E11" t="n">
-        <v>20.975</v>
+        <v>21.599</v>
       </c>
       <c r="F11" t="n">
         <v>5.0726</v>
@@ -1312,13 +1312,13 @@
         <v>17.8401</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.8268</v>
+        <v>-2.202900000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3785</v>
+        <v>4.0024</v>
       </c>
       <c r="U11" t="n">
-        <v>-6.2053</v>
+        <v>-6.2054</v>
       </c>
       <c r="V11" t="n">
         <v>4.6877</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7738</v>
+        <v>2.1695</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2829</v>
+        <v>4.4866</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5091</v>
+        <v>-2.3171</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1103</v>
@@ -1390,13 +1390,13 @@
         <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7276</v>
+        <v>1.1233</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5068</v>
+        <v>0.7105</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2208</v>
+        <v>0.4128</v>
       </c>
       <c r="V12" t="n">
         <v>2.7512</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7501</v>
+        <v>0.3027</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9201</v>
+        <v>0.3027</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.1174</v>
+        <v>0.3027</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3455</v>
+        <v>0.3027</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.772</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.2034</v>
+        <v>0.3027</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5857</v>
+        <v>0.3027</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.7891</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9141</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9312</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0171</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1253</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1057</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0195</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3027</v>
+        <v>-0.0559</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3027</v>
+        <v>1.7854</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-1.8413</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3027</v>
+        <v>3.2825</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3027</v>
+        <v>1.5453</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1.7372</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3027</v>
+        <v>2.5877</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3027</v>
+        <v>1.9371</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.6506</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.6948</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.3918</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.0866</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-1.1224</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.4147</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0.7077</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-3.0178</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2674</v>
+        <v>-0.2148</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1929</v>
+        <v>0.852</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9255</v>
+        <v>-1.0667</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2825</v>
+        <v>-0.4803</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5453</v>
+        <v>-0.4764</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7372</v>
+        <v>-0.0039</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5877</v>
+        <v>0.2416</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9371</v>
+        <v>0.1211</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6506</v>
+        <v>0.1205</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6948</v>
+        <v>-0.7219</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3918</v>
+        <v>-0.5975</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0866</v>
+        <v>-0.1244</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7991</v>
+        <v>0.4726</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0072</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7919</v>
+        <v>-0.1377</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.4142</v>
+        <v>-0.6036</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.0178</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6889</v>
+        <v>-1.1919</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5463</v>
+        <v>-0.4042</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2352</v>
+        <v>-0.7877</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4803</v>
+        <v>-3.1174</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4764</v>
+        <v>-0.3455</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0039</v>
+        <v>-2.772</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2416</v>
+        <v>-2.2034</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1211</v>
+        <v>0.5857</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1205</v>
+        <v>-2.7891</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7219</v>
+        <v>-0.9141</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5975</v>
+        <v>-0.9312</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1244</v>
+        <v>0.0171</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3964</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0014</v>
+        <v>2.1832</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3047</v>
+        <v>1.7814</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3062</v>
+        <v>0.4018</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6036</v>
+        <v>0.337</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6036</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5011</v>
+        <v>-1.3992</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0333</v>
+        <v>-0.9315</v>
       </c>
       <c r="F18" t="n">
         <v>-0.4677</v>
@@ -1858,10 +1858,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6984</v>
+        <v>-2.339</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3462</v>
+        <v>-1.263</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3522</v>
+        <v>-1.076</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4795</v>
@@ -1936,13 +1936,13 @@
         <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>0.358</v>
+        <v>-0.2826</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1749</v>
+        <v>0.258</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8169</v>
+        <v>-0.5406</v>
       </c>
       <c r="V19" t="n">
         <v>1.2071</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8146</v>
+        <v>-2.523</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2787</v>
+        <v>-0.9544</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5359</v>
+        <v>-1.5686</v>
       </c>
       <c r="G20" t="n">
         <v>-3.4196</v>
@@ -2014,13 +2014,13 @@
         <v>0.9911</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.395</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.121</v>
+        <v>1.2033</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.274</v>
+        <v>-0.3066</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4123</v>
+        <v>-3.5131</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9563</v>
+        <v>-2.1414</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.456</v>
+        <v>-1.3718</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9362</v>
@@ -2092,13 +2092,13 @@
         <v>0.9911</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2779</v>
+        <v>0.6213</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3782</v>
+        <v>1.1931</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6561</v>
+        <v>-0.5718</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8945</v>
+        <v>-4.2532</v>
       </c>
       <c r="E22" t="n">
         <v>1.7484</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.6428</v>
+        <v>-6.0016</v>
       </c>
       <c r="G22" t="n">
         <v>-0.841</v>
@@ -2170,13 +2170,13 @@
         <v>1.5858</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8265</v>
+        <v>-0.1853</v>
       </c>
       <c r="T22" t="n">
         <v>0.1948</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0213</v>
+        <v>-0.3801</v>
       </c>
       <c r="V22" t="n">
         <v>-3.4252</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.7127</v>
+        <v>-6.6157</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8041</v>
+        <v>-4.9517</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9087</v>
+        <v>-1.6641</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.9874</v>
+        <v>-1.523</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5743</v>
+        <v>-2.0069</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.413</v>
+        <v>0.4839</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.9211</v>
+        <v>-1.426</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.968</v>
+        <v>-0.9478</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9531</v>
+        <v>-0.4782</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.0662</v>
+        <v>-0.097</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6064</v>
+        <v>-1.0591</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4599</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9822</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q23" t="n">
         <v>-3.1716</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1864</v>
+        <v>-0.8966</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2886</v>
+        <v>-0.354</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1022</v>
+        <v>-0.5425</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0704</v>
+        <v>-2.6104</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0704</v>
+        <v>-2.6104</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.9272</v>
+        <v>-7.243</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1554</v>
+        <v>-5.1097</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7718</v>
+        <v>-2.1333</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.523</v>
+        <v>-5.9874</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0069</v>
+        <v>-2.5743</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4839</v>
+        <v>-3.413</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.426</v>
+        <v>-2.9211</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9478</v>
+        <v>-0.968</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4782</v>
+        <v>-1.9531</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.097</v>
+        <v>-3.0662</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0591</v>
+        <v>-1.6064</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9622000000000001</v>
+        <v>-1.4599</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5858</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q24" t="n">
         <v>-3.1716</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5858</v>
+        <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2081</v>
+        <v>0.6562</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5578</v>
+        <v>0.983</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6503</v>
+        <v>-0.3268</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.6104</v>
+        <v>0.0704</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.6104</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-26.0477</v>
+        <v>-25.3686</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.072700000000001</v>
+        <v>-5.072799999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-20.9749</v>
+        <v>-20.2959</v>
       </c>
       <c r="G25" t="n">
         <v>-17.249</v>
@@ -2383,7 +2383,7 @@
         <v>3.548900000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.6326</v>
+        <v>-5.632600000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-15.1654</v>
@@ -2404,13 +2404,13 @@
         <v>10.9022</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8269</v>
+        <v>3.5059</v>
       </c>
       <c r="T25" t="n">
         <v>6.205299999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.3786</v>
+        <v>-2.6992</v>
       </c>
       <c r="V25" t="n">
         <v>-4.6877</v>
